--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -44126,13 +44126,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="O243" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R243" t="n">
-        <v>0.3255789471970637</v>
+        <v>0.3217030073494796</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -44285,10 +44285,10 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="O244" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
@@ -46040,13 +46040,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O254" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R254" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -46204,10 +46204,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O255" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -46443,13 +46443,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O256" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="R256" t="n">
-        <v>0.03488345862825683</v>
+        <v>0.04263533832342501</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -46602,10 +46602,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O257" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>585451</v>
+        <v>585456</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -43723,13 +43723,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O241" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R241" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -43887,10 +43887,10 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O242" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
@@ -44126,13 +44126,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O243" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R243" t="n">
-        <v>0.3217030073494796</v>
+        <v>0.3197650374256876</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -44285,10 +44285,10 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O244" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
@@ -45608,12 +45608,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -45638,104 +45638,90 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N252" t="n">
+        <v>164</v>
+      </c>
+      <c r="O252" t="n">
+        <v>164</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0.1339565788407857</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
+      <c r="AT252" t="n">
         <v>0</v>
       </c>
-      <c r="O252" t="n">
-        <v>0</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0</v>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO252" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP252" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ252" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="AT252" t="n">
-        <v>1</v>
-      </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45762,7 +45748,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -45811,98 +45797,23 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
+      <c r="R253" t="n">
+        <v>0</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U253" t="inlineStr">
         <is>
           <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
         </is>
       </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>Syphilis</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Australia NINDSS unqualified syphilis category retained separately from duration-qualified and congenital series.</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN253" t="b">
-        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
@@ -45996,17 +45907,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -46040,22 +45951,39 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
-        <v>5</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.08894045854320688</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -46063,77 +45991,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Australia NINDSS unqualified syphilis category retained separately from duration-qualified and congenital series.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
         </is>
       </c>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46160,7 +46141,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -46209,98 +46190,23 @@
       <c r="O255" t="n">
         <v>5</v>
       </c>
+      <c r="R255" t="n">
+        <v>0.08894045854320688</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U255" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Syphilis</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
@@ -46399,17 +46305,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -46443,22 +46349,39 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="O256" t="n">
-        <v>22</v>
-      </c>
-      <c r="R256" t="n">
-        <v>0.04263533832342501</v>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -46466,6 +46389,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN256" t="b">
+        <v>1</v>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46473,65 +46454,70 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ256" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="AT256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46558,7 +46544,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -46602,103 +46588,28 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="O257" t="n">
-        <v>22</v>
+        <v>40</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0.07751879695168185</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U257" t="inlineStr">
         <is>
           <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>매독</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN257" t="b">
-        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
@@ -46792,17 +46703,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -46836,22 +46747,39 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0</v>
-      </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>40</v>
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>매독</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -46859,6 +46787,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN258" t="b">
+        <v>1</v>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46866,7 +46852,7 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
@@ -46874,62 +46860,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="AT258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -46956,7 +46937,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -47005,98 +46986,23 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
+      <c r="R259" t="n">
+        <v>0</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U259" t="inlineStr">
         <is>
           <t>SER_NO_FHI_903_MONTHLY</t>
         </is>
       </c>
-      <c r="V259" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W259" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X259" t="inlineStr">
-        <is>
-          <t>Syfilis</t>
-        </is>
-      </c>
-      <c r="Y259" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD259" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE259" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF259" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG259" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH259" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM259" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN259" t="b">
-        <v>1</v>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
@@ -47167,6 +47073,245 @@
         </is>
       </c>
       <c r="BC259" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>Syfilis</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM260" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN260" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP260" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV260" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA260" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB260" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC260" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47288,7 +47433,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -47298,7 +47443,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -47350,7 +47495,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>585456</v>
+        <v>585638</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -43723,13 +43723,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O241" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R241" t="n">
-        <v>0.2490332839209793</v>
+        <v>0.2668213756296206</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -43887,10 +43887,10 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O242" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
@@ -44126,13 +44126,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="O243" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="R243" t="n">
-        <v>0.3197650374256876</v>
+        <v>0.3275169171208557</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -44285,10 +44285,10 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="O244" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
@@ -44519,13 +44519,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O245" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R245" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.2653463738693259</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -44683,10 +44683,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O246" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
@@ -46185,13 +46185,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O255" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R255" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -46349,10 +46349,10 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O256" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U256" t="inlineStr">
         <is>
@@ -46588,13 +46588,13 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O257" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="R257" t="n">
-        <v>0.07751879695168185</v>
+        <v>0.09689849618960229</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -46747,10 +46747,10 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O258" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="U258" t="inlineStr">
         <is>
@@ -46981,13 +46981,13 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O259" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R259" t="n">
-        <v>0</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -47145,10 +47145,10 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U260" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>585638</v>
+        <v>585661</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -35619,7 +35619,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -42445,7 +42445,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -43684,12 +43684,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -43723,100 +43723,84 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>15</v>
+        <v>52981</v>
       </c>
       <c r="O241" t="n">
-        <v>15</v>
+        <v>52981</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>2</v>
       </c>
       <c r="R241" t="n">
-        <v>0.2668213756296206</v>
+        <v>3.749767974657717</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
-      <c r="AA241" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ241" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR241" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -43843,7 +43827,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -43892,98 +43876,23 @@
       <c r="O242" t="n">
         <v>15</v>
       </c>
+      <c r="R242" t="n">
+        <v>0.2668213756296206</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U242" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
-      <c r="V242" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
-      <c r="W242" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X242" t="inlineStr">
-        <is>
-          <t>Syphilis</t>
-        </is>
-      </c>
-      <c r="Y242" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD242" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE242" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF242" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG242" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH242" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI242" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ242" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK242" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
-        </is>
-      </c>
-      <c r="AM242" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN242" t="b">
-        <v>1</v>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
@@ -44082,17 +43991,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -44126,22 +44035,39 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>169</v>
+        <v>15</v>
       </c>
       <c r="O243" t="n">
-        <v>169</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0.3275169171208557</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -44149,6 +44075,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
+        </is>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN243" t="b">
+        <v>1</v>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44156,65 +44140,70 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ243" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="AT243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44241,7 +44230,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -44290,98 +44279,23 @@
       <c r="O244" t="n">
         <v>169</v>
       </c>
+      <c r="R244" t="n">
+        <v>0.3275169171208557</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U244" t="inlineStr">
         <is>
           <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>매독</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
@@ -44475,17 +44389,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -44519,22 +44433,39 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>15</v>
+        <v>169</v>
       </c>
       <c r="O245" t="n">
-        <v>15</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0.2653463738693259</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>169</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>매독</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -44542,6 +44473,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
+        <v>1</v>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44549,7 +44538,7 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ245" t="inlineStr">
@@ -44557,62 +44546,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="AT245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -44639,7 +44623,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -44688,98 +44672,23 @@
       <c r="O246" t="n">
         <v>15</v>
       </c>
+      <c r="R246" t="n">
+        <v>0.2653463738693259</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U246" t="inlineStr">
         <is>
           <t>SER_NO_FHI_903_MONTHLY</t>
         </is>
       </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W246" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X246" t="inlineStr">
-        <is>
-          <t>Syfilis</t>
-        </is>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE246" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF246" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG246" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK246" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM246" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN246" t="b">
-        <v>1</v>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
@@ -44878,17 +44787,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -44922,81 +44831,175 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>423</v>
+        <v>15</v>
       </c>
       <c r="O247" t="n">
-        <v>423</v>
-      </c>
-      <c r="R247" t="n">
-        <v>1.838227904842807</v>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>Syfilis</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN247" t="b">
+        <v>1</v>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45028,12 +45031,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -45058,7 +45061,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -45067,13 +45070,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>161</v>
+        <v>423</v>
       </c>
       <c r="O248" t="n">
-        <v>161</v>
+        <v>423</v>
       </c>
       <c r="R248" t="n">
-        <v>0.1315061536180884</v>
+        <v>1.838227904842807</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -45106,42 +45109,42 @@
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -45203,7 +45206,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -45212,13 +45215,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="O249" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="R249" t="n">
-        <v>0.1241548779499965</v>
+        <v>0.1315061536180884</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -45348,7 +45351,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -45357,13 +45360,13 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O250" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="R250" t="n">
-        <v>0.08576488279440546</v>
+        <v>0.1241548779499965</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -45493,7 +45496,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -45502,13 +45505,13 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="O251" t="n">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="R251" t="n">
-        <v>0.1592776394753244</v>
+        <v>0.08576488279440546</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -45638,7 +45641,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -45647,13 +45650,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="O252" t="n">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="R252" t="n">
-        <v>0.1339565788407857</v>
+        <v>0.1592776394753244</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -45753,12 +45756,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -45783,104 +45786,90 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N253" t="n">
+        <v>164</v>
+      </c>
+      <c r="O253" t="n">
+        <v>164</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0.1339565788407857</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr"/>
+      <c r="AT253" t="n">
         <v>0</v>
       </c>
-      <c r="O253" t="n">
-        <v>0</v>
-      </c>
-      <c r="R253" t="n">
-        <v>0</v>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="AA253" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP253" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ253" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="AT253" t="n">
-        <v>1</v>
-      </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45907,7 +45896,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -45956,98 +45945,23 @@
       <c r="O254" t="n">
         <v>0</v>
       </c>
+      <c r="R254" t="n">
+        <v>0</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U254" t="inlineStr">
         <is>
           <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
         </is>
       </c>
-      <c r="V254" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="W254" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X254" t="inlineStr">
-        <is>
-          <t>Syphilis</t>
-        </is>
-      </c>
-      <c r="Y254" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD254" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE254" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF254" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG254" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI254" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Australia NINDSS unqualified syphilis category retained separately from duration-qualified and congenital series.</t>
-        </is>
-      </c>
-      <c r="AM254" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN254" t="b">
-        <v>1</v>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
@@ -46141,17 +46055,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -46185,22 +46099,39 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
-        <v>6</v>
-      </c>
-      <c r="R255" t="n">
-        <v>0.1067285502518482</v>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -46208,77 +46139,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Australia NINDSS unqualified syphilis category retained separately from duration-qualified and congenital series.</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN255" t="b">
+        <v>1</v>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ255" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR255" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
         </is>
       </c>
       <c r="AT255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46305,7 +46289,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -46354,98 +46338,23 @@
       <c r="O256" t="n">
         <v>6</v>
       </c>
+      <c r="R256" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U256" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
-      <c r="V256" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
-      <c r="W256" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X256" t="inlineStr">
-        <is>
-          <t>Syphilis</t>
-        </is>
-      </c>
-      <c r="Y256" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD256" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE256" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF256" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG256" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI256" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ256" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK256" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
-        </is>
-      </c>
-      <c r="AM256" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN256" t="b">
-        <v>1</v>
       </c>
       <c r="AO256" t="inlineStr">
         <is>
@@ -46544,17 +46453,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -46588,22 +46497,39 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="O257" t="n">
-        <v>50</v>
-      </c>
-      <c r="R257" t="n">
-        <v>0.09689849618960229</v>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -46611,6 +46537,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
+        <v>1</v>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46618,65 +46602,70 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="AT257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46703,7 +46692,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -46752,98 +46741,23 @@
       <c r="O258" t="n">
         <v>50</v>
       </c>
+      <c r="R258" t="n">
+        <v>0.09689849618960229</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U258" t="inlineStr">
         <is>
           <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>매독</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE258" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF258" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG258" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
-        </is>
-      </c>
-      <c r="AM258" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN258" t="b">
-        <v>1</v>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
@@ -46937,17 +46851,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -46981,22 +46895,39 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="O259" t="n">
-        <v>2</v>
-      </c>
-      <c r="R259" t="n">
-        <v>0.03537951651591013</v>
-      </c>
-      <c r="S259" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>50</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>매독</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -47004,6 +46935,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
+        </is>
+      </c>
+      <c r="AM259" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN259" t="b">
+        <v>1</v>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47011,7 +47000,7 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
@@ -47019,62 +47008,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS259" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="AT259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -47101,7 +47085,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -47150,98 +47134,23 @@
       <c r="O260" t="n">
         <v>2</v>
       </c>
+      <c r="R260" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U260" t="inlineStr">
         <is>
           <t>SER_NO_FHI_903_MONTHLY</t>
         </is>
       </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>Syfilis</t>
-        </is>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG260" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK260" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM260" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN260" t="b">
-        <v>1</v>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
@@ -47312,6 +47221,245 @@
         </is>
       </c>
       <c r="BC260" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>2</v>
+      </c>
+      <c r="O261" t="n">
+        <v>2</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Syfilis</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN261" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV261" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB261" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC261" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47433,7 +47581,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -47443,7 +47591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -47495,7 +47643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>585661</v>
+        <v>638642</v>
       </c>
     </row>
     <row r="16">
@@ -47505,7 +47653,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -44274,13 +44274,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O244" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="R244" t="n">
-        <v>0.3275169171208557</v>
+        <v>0.3313928569684398</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -44433,10 +44433,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O245" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
@@ -46333,13 +46333,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O256" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R256" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -46497,10 +46497,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O257" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -46736,13 +46736,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="O258" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="R258" t="n">
-        <v>0.09689849618960229</v>
+        <v>0.1182161653513148</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -46895,10 +46895,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="O259" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>638642</v>
+        <v>638656</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -44274,13 +44274,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O244" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R244" t="n">
-        <v>0.3313928569684398</v>
+        <v>0.3333308268922319</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -44433,10 +44433,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O245" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
@@ -46333,13 +46333,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O256" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R256" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -46497,10 +46497,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O257" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -46736,13 +46736,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O258" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="R258" t="n">
-        <v>0.1182161653513148</v>
+        <v>0.1298439848940671</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -46895,10 +46895,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="O259" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
@@ -47462,6 +47462,151 @@
       <c r="BC261" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N262" t="n">
+        <v>162</v>
+      </c>
+      <c r="O262" t="n">
+        <v>162</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0.1323229620256541</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr"/>
+      <c r="AT262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV262" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA262" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB262" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC262" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47498,7 +47643,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -47581,7 +47726,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
@@ -47591,7 +47736,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11">
@@ -47643,7 +47788,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>638656</v>
+        <v>638827</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -44274,13 +44274,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O244" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R244" t="n">
-        <v>0.3333308268922319</v>
+        <v>0.337206766739816</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -44433,10 +44433,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O245" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
@@ -46736,13 +46736,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="O258" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="R258" t="n">
-        <v>0.1298439848940671</v>
+        <v>0.1608515036747398</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -46895,10 +46895,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="O259" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>638827</v>
+        <v>638845</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -47129,13 +47129,13 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O260" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R260" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -47293,10 +47293,10 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O261" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>638845</v>
+        <v>638847</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -46333,13 +46333,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O256" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R256" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -46497,10 +46497,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O257" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>638847</v>
+        <v>638849</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -46736,13 +46736,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="O258" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="R258" t="n">
-        <v>0.1608515036747398</v>
+        <v>0.1802312029126603</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -46895,10 +46895,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="O259" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>638849</v>
+        <v>638859</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -46736,13 +46736,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="O258" t="n">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="R258" t="n">
-        <v>0.1802312029126603</v>
+        <v>0.2170526314647091</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -46895,10 +46895,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="O259" t="n">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>638859</v>
+        <v>638878</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -21684,7 +21684,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -27392,7 +27392,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -28928,7 +28928,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -34088,7 +34088,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -35609,7 +35609,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -40769,7 +40769,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -42435,7 +42435,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -44515,7 +44515,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -46181,7 +46181,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -46333,13 +46333,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O256" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R256" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.3023975590469034</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -46497,10 +46497,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O257" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -46736,13 +46736,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="O258" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="R258" t="n">
-        <v>0.2170526314647091</v>
+        <v>0.2422462404740058</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -46895,10 +46895,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="O259" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -47129,13 +47129,13 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O260" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R260" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -47293,10 +47293,10 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O261" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
@@ -47605,6 +47605,151 @@
         </is>
       </c>
       <c r="BC262" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>163</v>
+      </c>
+      <c r="O263" t="n">
+        <v>163</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0.1331397704332199</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr"/>
+      <c r="AT263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV263" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA263" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB263" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC263" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -47643,7 +47788,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -47726,7 +47871,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
@@ -47736,7 +47881,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -47788,7 +47933,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>638878</v>
+        <v>639066</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -37776,12 +37776,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -37815,10 +37815,10 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>6440</v>
+        <v>2910</v>
       </c>
       <c r="O207" t="n">
-        <v>6440</v>
+        <v>2910</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
@@ -37927,12 +37927,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -37966,10 +37966,10 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>6440</v>
+        <v>2910</v>
       </c>
       <c r="O208" t="n">
-        <v>6440</v>
+        <v>2910</v>
       </c>
       <c r="U208" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr">
@@ -38124,7 +38124,7 @@
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
@@ -38161,12 +38161,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -38200,10 +38200,10 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>3705</v>
+        <v>6440</v>
       </c>
       <c r="O209" t="n">
-        <v>3705</v>
+        <v>6440</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
@@ -38312,12 +38312,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38351,10 +38351,10 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>3705</v>
+        <v>6440</v>
       </c>
       <c r="O210" t="n">
-        <v>3705</v>
+        <v>6440</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -38509,7 +38509,7 @@
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
@@ -38546,12 +38546,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38585,10 +38585,10 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>3273</v>
+        <v>3705</v>
       </c>
       <c r="O211" t="n">
-        <v>3273</v>
+        <v>3705</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
@@ -38697,12 +38697,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -38736,10 +38736,10 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>3273</v>
+        <v>3705</v>
       </c>
       <c r="O212" t="n">
-        <v>3273</v>
+        <v>3705</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -38894,7 +38894,7 @@
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
@@ -38931,12 +38931,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -38970,10 +38970,10 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>1208</v>
+        <v>3273</v>
       </c>
       <c r="O213" t="n">
-        <v>1208</v>
+        <v>3273</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
@@ -39082,12 +39082,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -39121,10 +39121,10 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>1208</v>
+        <v>3273</v>
       </c>
       <c r="O214" t="n">
-        <v>1208</v>
+        <v>3273</v>
       </c>
       <c r="U214" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -39279,7 +39279,7 @@
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
@@ -39316,12 +39316,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -39355,10 +39355,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>6078</v>
+        <v>1208</v>
       </c>
       <c r="O215" t="n">
-        <v>6078</v>
+        <v>1208</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
@@ -39467,12 +39467,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -39506,10 +39506,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>6078</v>
+        <v>1208</v>
       </c>
       <c r="O216" t="n">
-        <v>6078</v>
+        <v>1208</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -39664,7 +39664,7 @@
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
@@ -39701,12 +39701,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -39740,10 +39740,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>1105</v>
+        <v>6078</v>
       </c>
       <c r="O217" t="n">
-        <v>1105</v>
+        <v>6078</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
@@ -39852,12 +39852,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -39891,10 +39891,10 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>1105</v>
+        <v>6078</v>
       </c>
       <c r="O218" t="n">
-        <v>1105</v>
+        <v>6078</v>
       </c>
       <c r="U218" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -40049,7 +40049,7 @@
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
@@ -40086,12 +40086,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -40125,22 +40125,14 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>13</v>
+        <v>1105</v>
       </c>
       <c r="O219" t="n">
-        <v>13</v>
-      </c>
-      <c r="R219" t="n">
-        <v>0.2312451922123379</v>
+        <v>1105</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -40155,22 +40147,17 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="AT219" t="n">
@@ -40178,47 +40165,47 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -40250,12 +40237,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -40289,29 +40276,29 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>13</v>
+        <v>1105</v>
       </c>
       <c r="O220" t="n">
-        <v>13</v>
+        <v>1105</v>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>Syphilis</t>
+          <t>梅毒</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
@@ -40321,7 +40308,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -40336,7 +40323,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -40371,17 +40358,17 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -40394,22 +40381,17 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="AT220" t="n">
@@ -40417,47 +40399,47 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -40489,12 +40471,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -40528,13 +40510,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>189</v>
+        <v>13</v>
       </c>
       <c r="O221" t="n">
-        <v>189</v>
+        <v>13</v>
       </c>
       <c r="R221" t="n">
-        <v>0.3662763155966967</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -40543,7 +40525,7 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -40558,65 +40540,70 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="AT221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -40648,12 +40635,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -40687,29 +40674,29 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>189</v>
+        <v>13</v>
       </c>
       <c r="O222" t="n">
-        <v>189</v>
+        <v>13</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>매독</t>
+          <t>Syphilis</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -40719,7 +40706,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -40734,7 +40721,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -40749,7 +40736,7 @@
       </c>
       <c r="AF222" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG222" t="inlineStr">
@@ -40769,12 +40756,12 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
@@ -40792,65 +40779,70 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="AT222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -40882,12 +40874,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -40921,13 +40913,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>10</v>
+        <v>189</v>
       </c>
       <c r="O223" t="n">
-        <v>10</v>
+        <v>189</v>
       </c>
       <c r="R223" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.3662763155966967</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -40936,7 +40928,7 @@
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -40951,7 +40943,7 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
@@ -40959,62 +40951,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="AT223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -41046,12 +41033,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -41085,29 +41072,29 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>10</v>
+        <v>189</v>
       </c>
       <c r="O224" t="n">
-        <v>10</v>
+        <v>189</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>Syfilis</t>
+          <t>매독</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -41117,7 +41104,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -41132,7 +41119,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -41147,7 +41134,7 @@
       </c>
       <c r="AF224" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG224" t="inlineStr">
@@ -41167,17 +41154,17 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -41190,7 +41177,7 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
@@ -41198,62 +41185,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="AT224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -41285,12 +41267,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -41324,81 +41306,100 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="O225" t="n">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="R225" t="n">
-        <v>4.389149370901265</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -41425,17 +41426,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -41460,7 +41461,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -41469,81 +41470,175 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>172</v>
+        <v>10</v>
       </c>
       <c r="O226" t="n">
-        <v>172</v>
-      </c>
-      <c r="R226" t="n">
-        <v>0.1404910461013118</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Syfilis</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -41575,12 +41670,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -41605,7 +41700,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -41614,13 +41709,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>183</v>
+        <v>1010</v>
       </c>
       <c r="O227" t="n">
-        <v>183</v>
+        <v>1010</v>
       </c>
       <c r="R227" t="n">
-        <v>0.1494759385845352</v>
+        <v>4.389149370901265</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -41653,42 +41748,42 @@
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -41750,7 +41845,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -41759,13 +41854,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="O228" t="n">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="R228" t="n">
-        <v>0.1331397704332199</v>
+        <v>0.1404910461013118</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -41895,7 +41990,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -41904,13 +41999,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="O229" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="R229" t="n">
-        <v>0.1413078545088776</v>
+        <v>0.1494759385845352</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -42040,7 +42135,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -42049,13 +42144,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="O230" t="n">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="R230" t="n">
-        <v>0.1053682845759838</v>
+        <v>0.1331397704332199</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -42155,12 +42250,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -42185,104 +42280,90 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N231" t="n">
+        <v>173</v>
+      </c>
+      <c r="O231" t="n">
+        <v>173</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0.1413078545088776</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
+      <c r="AT231" t="n">
         <v>0</v>
       </c>
-      <c r="O231" t="n">
-        <v>0</v>
-      </c>
-      <c r="R231" t="n">
-        <v>0</v>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO231" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP231" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="AT231" t="n">
-        <v>1</v>
-      </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42309,17 +42390,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -42344,179 +42425,90 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N232" t="n">
+        <v>129</v>
+      </c>
+      <c r="O232" t="n">
+        <v>129</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0.1053682845759838</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
+      <c r="AT232" t="n">
         <v>0</v>
       </c>
-      <c r="O232" t="n">
-        <v>0</v>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Syphilis</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Australia NINDSS unqualified syphilis category retained separately from duration-qualified and congenital series.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO232" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP232" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
-        </is>
-      </c>
-      <c r="AT232" t="n">
-        <v>1</v>
-      </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42548,12 +42540,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -42592,33 +42584,50 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
+      <c r="R233" t="n">
+        <v>0</v>
+      </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
@@ -42628,12 +42637,12 @@
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
@@ -42648,12 +42657,12 @@
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
@@ -42685,17 +42694,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -42734,33 +42743,125 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Australia NINDSS unqualified syphilis category retained separately from duration-qualified and congenital series.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>1</v>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
@@ -42770,12 +42871,12 @@
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
@@ -42790,12 +42891,12 @@
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
@@ -42832,12 +42933,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -42912,7 +43013,7 @@
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
@@ -42932,7 +43033,7 @@
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
@@ -42974,12 +43075,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -43054,7 +43155,7 @@
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
@@ -43074,7 +43175,7 @@
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
@@ -43116,12 +43217,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -43196,7 +43297,7 @@
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
@@ -43216,7 +43317,7 @@
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
@@ -43258,12 +43359,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -43338,7 +43439,7 @@
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
@@ -43358,7 +43459,7 @@
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
@@ -43400,12 +43501,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -43480,7 +43581,7 @@
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
@@ -43500,7 +43601,7 @@
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
@@ -43542,12 +43643,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -43622,7 +43723,7 @@
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
@@ -43642,7 +43743,7 @@
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
@@ -43684,12 +43785,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -43723,20 +43824,14 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>52981</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
-        <v>52981</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>2</v>
-      </c>
-      <c r="R241" t="n">
-        <v>3.749767974657717</v>
+        <v>0</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
@@ -43765,42 +43860,42 @@
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -43832,12 +43927,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43871,100 +43966,78 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
-        <v>15</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0.2668213756296206</v>
+        <v>0</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
-      <c r="AA242" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ242" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR242" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -43991,17 +44064,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -44035,175 +44108,84 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>15</v>
+        <v>52981</v>
       </c>
       <c r="O243" t="n">
-        <v>15</v>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
-      <c r="W243" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>Syphilis</t>
-        </is>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE243" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF243" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG243" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ243" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK243" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
-        </is>
-      </c>
-      <c r="AM243" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN243" t="b">
-        <v>1</v>
+        <v>52981</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>2</v>
+      </c>
+      <c r="R243" t="n">
+        <v>3.749767974657717</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR243" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -44235,12 +44217,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -44274,22 +44256,14 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>174</v>
+        <v>1835</v>
       </c>
       <c r="O244" t="n">
-        <v>174</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0.337206766739816</v>
+        <v>1835</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -44304,7 +44278,7 @@
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ244" t="inlineStr">
@@ -44314,55 +44288,55 @@
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="AT244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -44394,12 +44368,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -44433,29 +44407,29 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>174</v>
+        <v>1835</v>
       </c>
       <c r="O245" t="n">
-        <v>174</v>
+        <v>1835</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
         <is>
-          <t>매독</t>
+          <t>梅毒</t>
         </is>
       </c>
       <c r="Y245" t="inlineStr">
@@ -44465,7 +44439,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -44480,7 +44454,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -44495,7 +44469,7 @@
       </c>
       <c r="AF245" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG245" t="inlineStr">
@@ -44515,17 +44489,17 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -44538,7 +44512,7 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ245" t="inlineStr">
@@ -44548,55 +44522,55 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="AT245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -44628,12 +44602,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -44667,22 +44641,14 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>15</v>
+        <v>5776</v>
       </c>
       <c r="O246" t="n">
-        <v>15</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0.2653463738693259</v>
+        <v>5776</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -44697,7 +44663,7 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ246" t="inlineStr">
@@ -44705,14 +44671,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="AT246" t="n">
@@ -44720,47 +44681,47 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -44792,12 +44753,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -44831,29 +44792,29 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>15</v>
+        <v>5776</v>
       </c>
       <c r="O247" t="n">
-        <v>15</v>
+        <v>5776</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
         <is>
-          <t>Syfilis</t>
+          <t>梅毒</t>
         </is>
       </c>
       <c r="Y247" t="inlineStr">
@@ -44863,7 +44824,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -44878,7 +44839,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -44913,17 +44874,17 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -44936,7 +44897,7 @@
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ247" t="inlineStr">
@@ -44944,14 +44905,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="AT247" t="n">
@@ -44959,47 +44915,47 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45031,12 +44987,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -45070,81 +45026,87 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>423</v>
+        <v>3360</v>
       </c>
       <c r="O248" t="n">
-        <v>423</v>
-      </c>
-      <c r="R248" t="n">
-        <v>1.838227904842807</v>
+        <v>3360</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45171,17 +45133,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -45206,7 +45168,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -45215,81 +45177,170 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>161</v>
+        <v>3360</v>
       </c>
       <c r="O249" t="n">
-        <v>161</v>
-      </c>
-      <c r="R249" t="n">
-        <v>0.1315061536180884</v>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3360</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>country:CN-HN:national</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN249" t="b">
+        <v>1</v>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45321,12 +45372,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -45351,7 +45402,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -45360,81 +45411,87 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>152</v>
+        <v>2922</v>
       </c>
       <c r="O250" t="n">
-        <v>152</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0.1241548779499965</v>
+        <v>2922</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45461,17 +45518,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -45496,7 +45553,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -45505,81 +45562,170 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>105</v>
+        <v>2922</v>
       </c>
       <c r="O251" t="n">
-        <v>105</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0.08576488279440546</v>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2922</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45611,12 +45757,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -45641,7 +45787,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -45650,81 +45796,87 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>195</v>
+        <v>1097</v>
       </c>
       <c r="O252" t="n">
-        <v>195</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.1592776394753244</v>
+        <v>1097</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45751,17 +45903,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -45786,7 +45938,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -45795,81 +45947,170 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>164</v>
+        <v>1097</v>
       </c>
       <c r="O253" t="n">
-        <v>164</v>
-      </c>
-      <c r="R253" t="n">
-        <v>0.1339565788407857</v>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1097</v>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN253" t="b">
+        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45901,12 +46142,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -45931,31 +46172,23 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>5855</v>
       </c>
       <c r="O254" t="n">
-        <v>0</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0</v>
+        <v>5855</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -45965,70 +46198,70 @@
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="AT254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46060,12 +46293,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -46090,38 +46323,38 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>5855</v>
       </c>
       <c r="O255" t="n">
-        <v>0</v>
+        <v>5855</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X255" t="inlineStr">
         <is>
-          <t>Syphilis</t>
+          <t>梅毒</t>
         </is>
       </c>
       <c r="Y255" t="inlineStr">
@@ -46131,7 +46364,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -46146,7 +46379,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -46161,7 +46394,7 @@
       </c>
       <c r="AF255" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG255" t="inlineStr">
@@ -46181,12 +46414,12 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>Australia NINDSS unqualified syphilis category retained separately from duration-qualified and congenital series.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM255" t="inlineStr">
@@ -46199,70 +46432,70 @@
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ255" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr">
         <is>
-          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="AT255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46294,12 +46527,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -46324,31 +46557,23 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N256" t="n">
-        <v>17</v>
+        <v>1042</v>
       </c>
       <c r="O256" t="n">
-        <v>17</v>
-      </c>
-      <c r="R256" t="n">
-        <v>0.3023975590469034</v>
+        <v>1042</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -46363,22 +46588,17 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ256" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="AT256" t="n">
@@ -46386,47 +46606,47 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46458,12 +46678,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -46488,38 +46708,38 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N257" t="n">
-        <v>17</v>
+        <v>1042</v>
       </c>
       <c r="O257" t="n">
-        <v>17</v>
+        <v>1042</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>Syphilis</t>
+          <t>梅毒</t>
         </is>
       </c>
       <c r="Y257" t="inlineStr">
@@ -46529,7 +46749,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -46544,7 +46764,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -46579,17 +46799,17 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -46602,22 +46822,17 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_116</t>
+          <t>SER_CN_PROV_DC_SYPHILIS; SER_CN_PROV_REPORT_SYPHILIS</t>
         </is>
       </c>
       <c r="AT257" t="n">
@@ -46625,47 +46840,47 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -46697,12 +46912,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -46727,22 +46942,22 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N258" t="n">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="O258" t="n">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="R258" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.2668213756296206</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -46751,7 +46966,7 @@
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -46766,65 +46981,70 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="AT258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46856,12 +47076,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -46886,38 +47106,38 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N259" t="n">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="O259" t="n">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X259" t="inlineStr">
         <is>
-          <t>매독</t>
+          <t>Syphilis</t>
         </is>
       </c>
       <c r="Y259" t="inlineStr">
@@ -46927,7 +47147,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -46942,7 +47162,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -46957,7 +47177,7 @@
       </c>
       <c r="AF259" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG259" t="inlineStr">
@@ -46977,12 +47197,12 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
         </is>
       </c>
       <c r="AM259" t="inlineStr">
@@ -47000,65 +47220,70 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr">
         <is>
-          <t>SER_KR_SYPHILIS_TOTAL</t>
+          <t>SER_FI_THL_TTR_116</t>
         </is>
       </c>
       <c r="AT259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47090,12 +47315,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -47120,22 +47345,22 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N260" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="O260" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="R260" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.337206766739816</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -47144,7 +47369,7 @@
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -47159,7 +47384,7 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
@@ -47167,62 +47392,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS260" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="AT260" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -47254,12 +47474,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -47284,38 +47504,38 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N261" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="O261" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X261" t="inlineStr">
         <is>
-          <t>Syfilis</t>
+          <t>매독</t>
         </is>
       </c>
       <c r="Y261" t="inlineStr">
@@ -47325,7 +47545,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -47340,7 +47560,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -47355,7 +47575,7 @@
       </c>
       <c r="AF261" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG261" t="inlineStr">
@@ -47375,17 +47595,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
         </is>
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -47398,7 +47618,7 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
@@ -47406,62 +47626,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS261" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_903_MONTHLY</t>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
         </is>
       </c>
       <c r="AT261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -47493,12 +47708,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -47523,90 +47738,109 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N262" t="n">
-        <v>162</v>
+        <v>15</v>
       </c>
       <c r="O262" t="n">
-        <v>162</v>
+        <v>15</v>
       </c>
       <c r="R262" t="n">
-        <v>0.1323229620256541</v>
+        <v>0.2653463738693259</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR262" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -47633,123 +47867,2969 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>15</v>
+      </c>
+      <c r="O263" t="n">
+        <v>15</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>Syfilis</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN263" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV263" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA263" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB263" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC263" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N264" t="n">
+        <v>423</v>
+      </c>
+      <c r="O264" t="n">
+        <v>423</v>
+      </c>
+      <c r="R264" t="n">
+        <v>1.838227904842807</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr"/>
+      <c r="AT264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV264" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA264" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB264" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC264" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="G265" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>D034</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>Syphilis</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
         <is>
           <t>梅毒</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="K265" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr">
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N265" t="n">
+        <v>161</v>
+      </c>
+      <c r="O265" t="n">
+        <v>161</v>
+      </c>
+      <c r="R265" t="n">
+        <v>0.1315061536180884</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr"/>
+      <c r="AT265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV265" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA265" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB265" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC265" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>152</v>
+      </c>
+      <c r="O266" t="n">
+        <v>152</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0.1241548779499965</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO266" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP266" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr"/>
+      <c r="AT266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU266" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV266" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA266" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB266" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC266" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N267" t="n">
+        <v>105</v>
+      </c>
+      <c r="O267" t="n">
+        <v>105</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0.08576488279440546</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
+      <c r="AT267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV267" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA267" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB267" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC267" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N268" t="n">
+        <v>195</v>
+      </c>
+      <c r="O268" t="n">
+        <v>195</v>
+      </c>
+      <c r="R268" t="n">
+        <v>0.1592776394753244</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO268" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP268" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
+      <c r="AT268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU268" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV268" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA268" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB268" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC268" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N269" t="n">
+        <v>164</v>
+      </c>
+      <c r="O269" t="n">
+        <v>164</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0.1339565788407857</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr"/>
+      <c r="AT269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU269" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV269" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA269" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB269" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC269" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="AT270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA270" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB270" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC270" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>Australia NINDSS unqualified syphilis category retained separately from duration-qualified and congenital series.</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN271" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_UNQUALIFIED</t>
+        </is>
+      </c>
+      <c r="AT271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA271" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB271" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC271" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>17</v>
+      </c>
+      <c r="O272" t="n">
+        <v>17</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.3023975590469034</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="AT272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV272" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA272" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB272" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC272" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>17</v>
+      </c>
+      <c r="O273" t="n">
+        <v>17</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="AT273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV273" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA273" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB273" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC273" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>125</v>
+      </c>
+      <c r="O274" t="n">
+        <v>125</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0.2422462404740058</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="AT274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>125</v>
+      </c>
+      <c r="O275" t="n">
+        <v>125</v>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>매독</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
+        </is>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN275" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="AT275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV275" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA275" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB275" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC275" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>10</v>
+      </c>
+      <c r="O276" t="n">
+        <v>10</v>
+      </c>
+      <c r="R276" t="n">
+        <v>0.1768975825795506</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV276" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>10</v>
+      </c>
+      <c r="O277" t="n">
+        <v>10</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>Syfilis</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN277" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_903_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV277" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA277" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB277" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC277" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N278" t="n">
+        <v>162</v>
+      </c>
+      <c r="O278" t="n">
+        <v>162</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0.1323229620256541</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr"/>
+      <c r="AT278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV278" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA278" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB278" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC278" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="M263" t="inlineStr">
+      <c r="M279" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N263" t="n">
+      <c r="N279" t="n">
         <v>163</v>
       </c>
-      <c r="O263" t="n">
+      <c r="O279" t="n">
         <v>163</v>
       </c>
-      <c r="R263" t="n">
+      <c r="R279" t="n">
         <v>0.1331397704332199</v>
       </c>
-      <c r="S263" t="inlineStr">
+      <c r="S279" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO263" t="inlineStr">
+      <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP263" t="inlineStr">
+      <c r="AP279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR263" t="inlineStr">
+      <c r="AR279" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS263" t="inlineStr"/>
-      <c r="AT263" t="n">
+      <c r="AS279" t="inlineStr"/>
+      <c r="AT279" t="n">
         <v>0</v>
       </c>
-      <c r="AU263" t="inlineStr">
+      <c r="AU279" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV263" t="inlineStr">
+      <c r="AV279" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW263" t="inlineStr">
+      <c r="AW279" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX263" t="inlineStr">
+      <c r="AX279" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY263" t="inlineStr">
+      <c r="AY279" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ263" t="inlineStr">
+      <c r="AZ279" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA263" t="inlineStr">
+      <c r="BA279" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB263" t="inlineStr">
+      <c r="BB279" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC263" t="inlineStr">
+      <c r="BC279" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -47871,7 +50951,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -47881,7 +50961,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>262</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11">
@@ -47901,7 +50981,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -47933,7 +51013,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>639066</v>
+        <v>663863</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -40913,13 +40913,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O223" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R223" t="n">
-        <v>0.3662763155966967</v>
+        <v>0.3643383456729046</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -41072,10 +41072,10 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O224" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
@@ -49413,13 +49413,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O272" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R272" t="n">
-        <v>0.3023975590469034</v>
+        <v>0.3379737424641861</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -49577,10 +49577,10 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O273" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="U273" t="inlineStr">
         <is>
@@ -49816,13 +49816,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="O274" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="R274" t="n">
-        <v>0.2422462404740058</v>
+        <v>0.3023233081115592</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -49975,10 +49975,10 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="O275" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
@@ -50832,6 +50832,947 @@
       <c r="BC279" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>146</v>
+      </c>
+      <c r="O280" t="n">
+        <v>146</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0.1192540275046019</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr"/>
+      <c r="AT280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
+      <c r="R281" t="n">
+        <v>0</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="AT281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ282" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 116.</t>
+        </is>
+      </c>
+      <c r="AM282" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN282" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_116</t>
+        </is>
+      </c>
+      <c r="AT282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>5</v>
+      </c>
+      <c r="O283" t="n">
+        <v>5</v>
+      </c>
+      <c r="R283" t="n">
+        <v>0.009689849618960231</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="AT283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>5</v>
+      </c>
+      <c r="O284" t="n">
+        <v>5</v>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>매독</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ284" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK284" t="inlineStr">
+        <is>
+          <t>Korea KDCA aggregate acquired syphilis notifications; congenital syphilis is reported separately.</t>
+        </is>
+      </c>
+      <c r="AM284" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN284" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>SER_KR_SYPHILIS_TOTAL</t>
+        </is>
+      </c>
+      <c r="AT284" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -50868,7 +51809,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -50951,7 +51892,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -50961,7 +51902,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
@@ -50981,7 +51922,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -51013,7 +51954,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>663863</v>
+        <v>664046</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -27800,7 +27800,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -34496,7 +34496,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -41562,7 +41562,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -48003,7 +48003,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -50209,13 +50209,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O276" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R276" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -50373,10 +50373,10 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O277" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
@@ -50465,7 +50465,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -51954,7 +51954,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>664046</v>
+        <v>664052</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -74704,13 +74704,13 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O394" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R394" t="n">
-        <v>0.3081372178829353</v>
+        <v>0.3100751878067274</v>
       </c>
       <c r="S394" t="inlineStr">
         <is>
@@ -74863,10 +74863,10 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O395" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U395" t="inlineStr">
         <is>
@@ -76483,13 +76483,13 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O404" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R404" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S404" t="inlineStr">
         <is>
@@ -76642,10 +76642,10 @@
         </is>
       </c>
       <c r="N405" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O405" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="U405" t="inlineStr">
         <is>
@@ -76987,7 +76987,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>664110</v>
+        <v>664120</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -74919,13 +74919,13 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="O395" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="R395" t="n">
-        <v>0.3100751878067274</v>
+        <v>0.3178270675018955</v>
       </c>
       <c r="S395" t="inlineStr">
         <is>
@@ -75078,10 +75078,10 @@
         </is>
       </c>
       <c r="N396" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="O396" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="U396" t="inlineStr">
         <is>
@@ -76295,13 +76295,13 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O403" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R403" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S403" t="inlineStr">
         <is>
@@ -76459,10 +76459,10 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O404" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U404" t="inlineStr">
         <is>
@@ -76698,13 +76698,13 @@
         </is>
       </c>
       <c r="N405" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="O405" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="R405" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.06007706763755342</v>
       </c>
       <c r="S405" t="inlineStr">
         <is>
@@ -76857,10 +76857,10 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="O406" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="U406" t="inlineStr">
         <is>
@@ -77605,7 +77605,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>664250</v>
+        <v>664263</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d034/2026-2029.xlsx
+++ b/diseases/d034/2026-2029.xlsx
@@ -74919,13 +74919,13 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O395" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R395" t="n">
-        <v>0.3178270675018955</v>
+        <v>0.3197650374256876</v>
       </c>
       <c r="S395" t="inlineStr">
         <is>
@@ -75078,10 +75078,10 @@
         </is>
       </c>
       <c r="N396" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O396" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="U396" t="inlineStr">
         <is>
@@ -75312,13 +75312,13 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O397" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R397" t="n">
-        <v>0.3007258903852361</v>
+        <v>0.3184156486431911</v>
       </c>
       <c r="S397" t="inlineStr">
         <is>
@@ -75476,10 +75476,10 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O398" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U398" t="inlineStr">
         <is>
@@ -76295,13 +76295,13 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O403" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R403" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S403" t="inlineStr">
         <is>
@@ -76459,10 +76459,10 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O404" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U404" t="inlineStr">
         <is>
@@ -76698,13 +76698,13 @@
         </is>
       </c>
       <c r="N405" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="O405" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="R405" t="n">
-        <v>0.06007706763755342</v>
+        <v>0.08720864657064206</v>
       </c>
       <c r="S405" t="inlineStr">
         <is>
@@ -76857,10 +76857,10 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="O406" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="U406" t="inlineStr">
         <is>
@@ -77091,13 +77091,13 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O407" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R407" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S407" t="inlineStr">
         <is>
@@ -77255,10 +77255,10 @@
         </is>
       </c>
       <c r="N408" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O408" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U408" t="inlineStr">
         <is>
@@ -77424,6 +77424,151 @@
       <c r="BC408" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>syphilis</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>D034</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Syphilis</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>梅毒</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N409" t="n">
+        <v>148</v>
+      </c>
+      <c r="O409" t="n">
+        <v>148</v>
+      </c>
+      <c r="R409" t="n">
+        <v>0.1208876443197334</v>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO409" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP409" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR409" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS409" t="inlineStr"/>
+      <c r="AT409" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU409" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV409" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW409" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX409" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY409" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA409" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB409" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC409" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77460,7 +77605,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -77543,7 +77688,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -77553,7 +77698,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11">
@@ -77605,7 +77750,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>664263</v>
+        <v>664436</v>
       </c>
     </row>
     <row r="16">
